--- a/apps_nicolo/NLDoseResponse_4s_6r_HF_REINFORCE copy/NLDoseResponse_4s_10r.xlsx
+++ b/apps_nicolo/NLDoseResponse_4s_6r_HF_REINFORCE copy/NLDoseResponse_4s_10r.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data'!$A$1:$Z$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data'!$A$1:$Z$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1545,8 +1545,360 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-12-18 18:16:03</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/nldoseresponse-4s-10r/21214c0309b041d2ae43092ff74d7c9c</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>300</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>(8, 5, 1, 1280)</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L13" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M13" t="n">
+        <v>128</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.005, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>30</v>
+      </c>
+      <c r="R13" t="n">
+        <v>100</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>20</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_independent'}</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.30207870105204454), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>{'sil_loss_weight': 1.0, 'sil_use_adaptive_baseline': False, 'sil_baseline_annealing_rate': 0.95}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-12-19 10:01:15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/nldoseresponse-4s-10r/3ae506ab324f48538b689594d86727c5</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>300</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>(4, 3, 1, 1280)</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L14" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M14" t="n">
+        <v>128</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.005, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>30</v>
+      </c>
+      <c r="R14" t="n">
+        <v>100</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>20</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_independent'}</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.3148360244717094), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>{'sil_loss_weight': 1.0, 'sil_use_adaptive_baseline': False, 'sil_baseline_annealing_rate': 0.95}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-12-19 10:24:57</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/nldoseresponse-4s-10r/8319fe87e1ad4cdf92db43cc57b0e1c7</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>300</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>(4, 3, 1, 1280)</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L15" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M15" t="n">
+        <v>128</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.005, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>30</v>
+      </c>
+      <c r="R15" t="n">
+        <v>100</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>30</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_independent'}</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.3148360244717094), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>{'sil_loss_weight': 1.0, 'sil_use_adaptive_baseline': False, 'sil_baseline_annealing_rate': 0.95}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-12-19 10:24:57</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/nldoseresponse-4s-10r/8319fe87e1ad4cdf92db43cc57b0e1c7</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>300</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>(4, 3, 1, 1280)</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L16" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M16" t="n">
+        <v>128</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.005, 'topk_entropy_weight': 1.0, 'remainder_entropy_weight': 1.0, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.0}</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>30</v>
+      </c>
+      <c r="R16" t="n">
+        <v>100</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>30</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_independent'}</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>{'structure': 2.0, 'continuous': 1.0, 'discrete': 0.0, 'input_influence': 0.0}</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>{'target_entropy_ratio_to_max': np.float64(0.3148360244717094), 'initial_temperature': 1.0, 'rate': 0.0, 'current_temperature': 1.0}</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>{'sil_loss_weight': 1.0, 'sil_use_adaptive_baseline': False, 'sil_baseline_annealing_rate': 0.95}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z12"/>
+  <autoFilter ref="A1:Z16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>